--- a/literature/matrix/literature_matrix.xlsx
+++ b/literature/matrix/literature_matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Research\Adaptive-RAG-Lab\literature\matrix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD671318-A212-41CC-920E-475789F454F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E107D8-DCB5-43AB-9941-50616F28D00A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -191,310 +191,294 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
+  <dxfs count="15">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -528,25 +512,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69C55FDA-FAFA-4BC7-897B-5C9327BF7B67}" name="Table1" displayName="Table1" ref="A1:P5" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A1:P5" xr:uid="{69C55FDA-FAFA-4BC7-897B-5C9327BF7B67}"/>
-  <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{679D3D90-9A89-4618-8CC8-7A86FE6FA1AE}" name="Column1" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{72104998-0AC0-4A1D-A3A7-50CD3B2D40DD}" name="Column2" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{38A42720-4B21-4E07-B4EF-702C8825CE50}" name="Column3" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{54AD448E-E9F4-4131-8404-BEC167281CF5}" name="Column4" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{D230C5A6-1163-47C0-9DD1-691A41D371C1}" name="Column5" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{5E7F9669-4FCF-4C87-9C40-9ABADB67D416}" name="Column6" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{FA66DECF-FA98-42F4-9108-713366B617A8}" name="Column7" dataDxfId="8"/>
-    <tableColumn id="8" xr3:uid="{1F7AB528-8BB9-4231-B183-A5B80AC8ED0C}" name="Column8" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{8739A737-0B47-4AF3-872E-3245AD5C6F65}" name="Column9" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{03BF5615-BD82-42DD-8759-FFCBBEF812D0}" name="Column10" dataDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{8FBD0AF8-2B73-41E6-91E0-FEC8A6E8A5DE}" name="Column11" dataDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{1AF66BE9-1FD6-4E70-961D-B109AC2ADA2D}" name="Column12" dataDxfId="3"/>
-    <tableColumn id="13" xr3:uid="{DA8FBC99-63EC-4797-BC7F-D07E928AAC42}" name="Column13" dataDxfId="2"/>
-    <tableColumn id="14" xr3:uid="{AD066A59-234F-41DC-B7EE-56B886F18511}" name="Column14" dataDxfId="1"/>
-    <tableColumn id="15" xr3:uid="{FC3DE1E0-5EC9-4A9F-B327-EE8AB3C01C12}" name="Column15" dataDxfId="0"/>
-    <tableColumn id="16" xr3:uid="{C61F479C-3AAA-4106-ADF9-5A01BC2EAF90}" name="Column16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69C55FDA-FAFA-4BC7-897B-5C9327BF7B67}" name="Table1" displayName="Table1" ref="A1:M5" totalsRowShown="0" headerRowDxfId="14" dataDxfId="0">
+  <autoFilter ref="A1:M5" xr:uid="{69C55FDA-FAFA-4BC7-897B-5C9327BF7B67}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{679D3D90-9A89-4618-8CC8-7A86FE6FA1AE}" name="Column1" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{72104998-0AC0-4A1D-A3A7-50CD3B2D40DD}" name="Column2" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{38A42720-4B21-4E07-B4EF-702C8825CE50}" name="Column3" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{54AD448E-E9F4-4131-8404-BEC167281CF5}" name="Column4" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{D230C5A6-1163-47C0-9DD1-691A41D371C1}" name="Column5" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{5E7F9669-4FCF-4C87-9C40-9ABADB67D416}" name="Column6" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{FA66DECF-FA98-42F4-9108-713366B617A8}" name="Column7" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{1F7AB528-8BB9-4231-B183-A5B80AC8ED0C}" name="Column8" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{8739A737-0B47-4AF3-872E-3245AD5C6F65}" name="Column9" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{03BF5615-BD82-42DD-8759-FFCBBEF812D0}" name="Column10" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{8FBD0AF8-2B73-41E6-91E0-FEC8A6E8A5DE}" name="Column11" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{1AF66BE9-1FD6-4E70-961D-B109AC2ADA2D}" name="Column12" dataDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{DA8FBC99-63EC-4797-BC7F-D07E928AAC42}" name="Column13" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -818,8 +799,18 @@
   <dimension ref="A1:P5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="9" width="10.44140625" customWidth="1"/>
-    <col min="10" max="15" width="11.44140625" customWidth="1"/>
+    <col min="1" max="1" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="10.44140625" customWidth="1"/>
+    <col min="9" max="9" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="11.44140625" customWidth="1"/>
     <col min="16" max="16" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -874,121 +865,126 @@
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="5"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:16" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="1">
+      <c r="C3" s="5"/>
+      <c r="D3" s="4">
         <v>2017</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="3"/>
-      <c r="H3" t="s">
+      <c r="G3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
+      <c r="I3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="5"/>
     </row>
-    <row r="4" spans="1:16" ht="144" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J4" t="s">
-        <v>36</v>
-      </c>
-      <c r="K4" s="3"/>
-      <c r="L4" t="s">
-        <v>38</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="5"/>
     </row>
-    <row r="5" spans="1:16" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/literature/matrix/literature_matrix.xlsx
+++ b/literature/matrix/literature_matrix.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30301"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30305"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Research\Adaptive-RAG-Lab\literature\matrix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E107D8-DCB5-43AB-9941-50616F28D00A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A50BCF50-F9F6-42B3-B514-B733660A6729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>ID</t>
   </si>
@@ -148,13 +148,34 @@
   </si>
   <si>
     <t>Finished</t>
+  </si>
+  <si>
+    <t>Assumptions</t>
+  </si>
+  <si>
+    <t>Open Questions</t>
+  </si>
+  <si>
+    <t>My Research Ideas</t>
+  </si>
+  <si>
+    <t>Priority (High/Medium/Low)</t>
+  </si>
+  <si>
+    <t>Column17</t>
+  </si>
+  <si>
+    <t>Column18</t>
+  </si>
+  <si>
+    <t>Column19</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -166,6 +187,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -191,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -206,14 +233,125 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="21">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -512,22 +650,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69C55FDA-FAFA-4BC7-897B-5C9327BF7B67}" name="Table1" displayName="Table1" ref="A1:M5" totalsRowShown="0" headerRowDxfId="14" dataDxfId="0">
-  <autoFilter ref="A1:M5" xr:uid="{69C55FDA-FAFA-4BC7-897B-5C9327BF7B67}"/>
-  <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{679D3D90-9A89-4618-8CC8-7A86FE6FA1AE}" name="Column1" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{72104998-0AC0-4A1D-A3A7-50CD3B2D40DD}" name="Column2" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{38A42720-4B21-4E07-B4EF-702C8825CE50}" name="Column3" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{54AD448E-E9F4-4131-8404-BEC167281CF5}" name="Column4" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{D230C5A6-1163-47C0-9DD1-691A41D371C1}" name="Column5" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{5E7F9669-4FCF-4C87-9C40-9ABADB67D416}" name="Column6" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{FA66DECF-FA98-42F4-9108-713366B617A8}" name="Column7" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{1F7AB528-8BB9-4231-B183-A5B80AC8ED0C}" name="Column8" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{8739A737-0B47-4AF3-872E-3245AD5C6F65}" name="Column9" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{03BF5615-BD82-42DD-8759-FFCBBEF812D0}" name="Column10" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{8FBD0AF8-2B73-41E6-91E0-FEC8A6E8A5DE}" name="Column11" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{1AF66BE9-1FD6-4E70-961D-B109AC2ADA2D}" name="Column12" dataDxfId="2"/>
-    <tableColumn id="13" xr3:uid="{DA8FBC99-63EC-4797-BC7F-D07E928AAC42}" name="Column13" dataDxfId="1"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69C55FDA-FAFA-4BC7-897B-5C9327BF7B67}" name="Table1" displayName="Table1" ref="A1:S5" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+  <autoFilter ref="A1:S5" xr:uid="{69C55FDA-FAFA-4BC7-897B-5C9327BF7B67}"/>
+  <tableColumns count="19">
+    <tableColumn id="1" xr3:uid="{679D3D90-9A89-4618-8CC8-7A86FE6FA1AE}" name="Column1" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{72104998-0AC0-4A1D-A3A7-50CD3B2D40DD}" name="Column2" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{38A42720-4B21-4E07-B4EF-702C8825CE50}" name="Column3" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{54AD448E-E9F4-4131-8404-BEC167281CF5}" name="Column4" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{D230C5A6-1163-47C0-9DD1-691A41D371C1}" name="Column5" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{5E7F9669-4FCF-4C87-9C40-9ABADB67D416}" name="Column6" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{FA66DECF-FA98-42F4-9108-713366B617A8}" name="Column7" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{1F7AB528-8BB9-4231-B183-A5B80AC8ED0C}" name="Column8" dataDxfId="11"/>
+    <tableColumn id="9" xr3:uid="{8739A737-0B47-4AF3-872E-3245AD5C6F65}" name="Column9" dataDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{03BF5615-BD82-42DD-8759-FFCBBEF812D0}" name="Column10" dataDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{8FBD0AF8-2B73-41E6-91E0-FEC8A6E8A5DE}" name="Column11" dataDxfId="8"/>
+    <tableColumn id="12" xr3:uid="{1AF66BE9-1FD6-4E70-961D-B109AC2ADA2D}" name="Column12" dataDxfId="7"/>
+    <tableColumn id="13" xr3:uid="{DA8FBC99-63EC-4797-BC7F-D07E928AAC42}" name="Column13" dataDxfId="6"/>
+    <tableColumn id="14" xr3:uid="{6013D486-8D83-4674-B8E8-BBA01F8D5182}" name="Column14" dataDxfId="5"/>
+    <tableColumn id="15" xr3:uid="{8E2F4043-643A-4C29-A6CF-D687803ADB46}" name="Column15" dataDxfId="4"/>
+    <tableColumn id="16" xr3:uid="{620F6A5A-1B54-49EC-B204-0A0387A762B6}" name="Column16" dataDxfId="3"/>
+    <tableColumn id="17" xr3:uid="{4FDEC39F-1170-4707-BF88-BA3F84BA31E2}" name="Column17" dataDxfId="2"/>
+    <tableColumn id="18" xr3:uid="{8BF0A9D8-6901-4BA9-93CB-35BA889098FF}" name="Column18" dataDxfId="1"/>
+    <tableColumn id="19" xr3:uid="{B729C20C-0AA0-4F13-9BC5-2698A61F320D}" name="Column19" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -796,7 +940,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.109375" bestFit="1" customWidth="1"/>
@@ -814,7 +958,7 @@
     <col min="16" max="16" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -860,11 +1004,20 @@
       <c r="O1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="Q1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -904,11 +1057,22 @@
       <c r="M2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="5"/>
+      <c r="N2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
     </row>
-    <row r="3" spans="1:16" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>29</v>
       </c>
@@ -937,10 +1101,10 @@
       <c r="J3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="5" t="s">
         <v>38</v>
       </c>
       <c r="M3" s="2" t="s">
@@ -948,9 +1112,12 @@
       </c>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
-      <c r="P3" s="5"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -966,9 +1133,12 @@
       <c r="M4" s="2"/>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
-      <c r="P4" s="5"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -984,9 +1154,13 @@
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
-      <c r="P5" s="5"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/literature/matrix/literature_matrix.xlsx
+++ b/literature/matrix/literature_matrix.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30305"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30309"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Research\Adaptive-RAG-Lab\literature\matrix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A50BCF50-F9F6-42B3-B514-B733660A6729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{897B6D0B-BDE7-4C57-8111-EE3DDAAF7858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$O$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$O$11</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
   <si>
     <t>ID</t>
   </si>
@@ -169,6 +169,21 @@
   </si>
   <si>
     <t>Column19</t>
+  </si>
+  <si>
+    <t>Retrieval-Augmented Generation for Knowledge-Intensive NLP Tasks</t>
+  </si>
+  <si>
+    <t>Reduced dependence on parametric memory</t>
+  </si>
+  <si>
+    <t>Fixed retrieval strategy, fixed Top-k, no confidence estimation, no reranking</t>
+  </si>
+  <si>
+    <t>Adaptive retrieval, confidence-aware retrieval, hybrid retrieval</t>
+  </si>
+  <si>
+    <t>.</t>
   </si>
 </sst>
 </file>
@@ -650,8 +665,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69C55FDA-FAFA-4BC7-897B-5C9327BF7B67}" name="Table1" displayName="Table1" ref="A1:S5" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
-  <autoFilter ref="A1:S5" xr:uid="{69C55FDA-FAFA-4BC7-897B-5C9327BF7B67}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69C55FDA-FAFA-4BC7-897B-5C9327BF7B67}" name="Table1" displayName="Table1" ref="A1:S11" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+  <autoFilter ref="A1:S11" xr:uid="{69C55FDA-FAFA-4BC7-897B-5C9327BF7B67}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{679D3D90-9A89-4618-8CC8-7A86FE6FA1AE}" name="Column1" dataDxfId="18"/>
     <tableColumn id="2" xr3:uid="{72104998-0AC0-4A1D-A3A7-50CD3B2D40DD}" name="Column2" dataDxfId="17"/>
@@ -940,25 +955,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.44140625" customWidth="1"/>
+    <col min="2" max="2" width="57.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="10.44140625" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" customWidth="1"/>
     <col min="9" max="9" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="53.77734375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="11.44140625" customWidth="1"/>
-    <col min="16" max="16" width="11.109375" customWidth="1"/>
+    <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="52.44140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -1017,7 +1036,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -1072,7 +1091,7 @@
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
     </row>
-    <row r="3" spans="1:19" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>29</v>
       </c>
@@ -1117,38 +1136,55 @@
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
+      <c r="B4" t="s">
+        <v>47</v>
+      </c>
       <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
+      <c r="D4">
+        <v>2020</v>
+      </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="4"/>
+      <c r="G4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="5"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="5"/>
+      <c r="K4" s="3"/>
+      <c r="L4" t="s">
+        <v>49</v>
+      </c>
       <c r="M4" s="2"/>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
+      <c r="P4" t="s">
+        <v>50</v>
+      </c>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
+      <c r="U4" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
+      <c r="G5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
+      <c r="J5" s="5"/>
       <c r="K5" s="3"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
@@ -1157,7 +1193,132 @@
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/literature/matrix/literature_matrix.xlsx
+++ b/literature/matrix/literature_matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Research\Adaptive-RAG-Lab\literature\matrix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{897B6D0B-BDE7-4C57-8111-EE3DDAAF7858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6D9AD28-7FF8-402D-AE07-0472C826828F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="41">
   <si>
     <t>ID</t>
   </si>
@@ -69,51 +69,6 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Column1</t>
-  </si>
-  <si>
-    <t>Column2</t>
-  </si>
-  <si>
-    <t>Column3</t>
-  </si>
-  <si>
-    <t>Column4</t>
-  </si>
-  <si>
-    <t>Column5</t>
-  </si>
-  <si>
-    <t>Column6</t>
-  </si>
-  <si>
-    <t>Column7</t>
-  </si>
-  <si>
-    <t>Column8</t>
-  </si>
-  <si>
-    <t>Column9</t>
-  </si>
-  <si>
-    <t>Column10</t>
-  </si>
-  <si>
-    <t>Column11</t>
-  </si>
-  <si>
-    <t>Column12</t>
-  </si>
-  <si>
-    <t>Column13</t>
-  </si>
-  <si>
-    <t>Column14</t>
-  </si>
-  <si>
-    <t>Column15</t>
-  </si>
-  <si>
     <t>Column16</t>
   </si>
   <si>
@@ -156,15 +111,9 @@
     <t>Open Questions</t>
   </si>
   <si>
-    <t>My Research Ideas</t>
-  </si>
-  <si>
     <t>Priority (High/Medium/Low)</t>
   </si>
   <si>
-    <t>Column17</t>
-  </si>
-  <si>
     <t>Column18</t>
   </si>
   <si>
@@ -184,6 +133,24 @@
   </si>
   <si>
     <t>.</t>
+  </si>
+  <si>
+    <t>Corrective Retrieval-Augmented Generation (CRAG)</t>
+  </si>
+  <si>
+    <t>Evaluates retrieval quality before generation and corrects poor retrieval</t>
+  </si>
+  <si>
+    <t>Prevents generation from poor evidence; supports web search and knowledge refinement</t>
+  </si>
+  <si>
+    <t>Build a decision engine that diagnoses the reason for low confidence and chooses the most appropriate adaptation instead of using a fixed correction pipeline</t>
+  </si>
+  <si>
+    <t>Retrieval quality can be reliably estimated and a predefined correction strategy is sufficient</t>
+  </si>
+  <si>
+    <t>Doesn't deeply analyze why retrieval failed; correction policy is relatively fixed</t>
   </si>
 </sst>
 </file>
@@ -668,23 +635,23 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69C55FDA-FAFA-4BC7-897B-5C9327BF7B67}" name="Table1" displayName="Table1" ref="A1:S11" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <autoFilter ref="A1:S11" xr:uid="{69C55FDA-FAFA-4BC7-897B-5C9327BF7B67}"/>
   <tableColumns count="19">
-    <tableColumn id="1" xr3:uid="{679D3D90-9A89-4618-8CC8-7A86FE6FA1AE}" name="Column1" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{72104998-0AC0-4A1D-A3A7-50CD3B2D40DD}" name="Column2" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{38A42720-4B21-4E07-B4EF-702C8825CE50}" name="Column3" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{54AD448E-E9F4-4131-8404-BEC167281CF5}" name="Column4" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{D230C5A6-1163-47C0-9DD1-691A41D371C1}" name="Column5" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{5E7F9669-4FCF-4C87-9C40-9ABADB67D416}" name="Column6" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{FA66DECF-FA98-42F4-9108-713366B617A8}" name="Column7" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{1F7AB528-8BB9-4231-B183-A5B80AC8ED0C}" name="Column8" dataDxfId="11"/>
-    <tableColumn id="9" xr3:uid="{8739A737-0B47-4AF3-872E-3245AD5C6F65}" name="Column9" dataDxfId="10"/>
-    <tableColumn id="10" xr3:uid="{03BF5615-BD82-42DD-8759-FFCBBEF812D0}" name="Column10" dataDxfId="9"/>
-    <tableColumn id="11" xr3:uid="{8FBD0AF8-2B73-41E6-91E0-FEC8A6E8A5DE}" name="Column11" dataDxfId="8"/>
-    <tableColumn id="12" xr3:uid="{1AF66BE9-1FD6-4E70-961D-B109AC2ADA2D}" name="Column12" dataDxfId="7"/>
-    <tableColumn id="13" xr3:uid="{DA8FBC99-63EC-4797-BC7F-D07E928AAC42}" name="Column13" dataDxfId="6"/>
-    <tableColumn id="14" xr3:uid="{6013D486-8D83-4674-B8E8-BBA01F8D5182}" name="Column14" dataDxfId="5"/>
-    <tableColumn id="15" xr3:uid="{8E2F4043-643A-4C29-A6CF-D687803ADB46}" name="Column15" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{679D3D90-9A89-4618-8CC8-7A86FE6FA1AE}" name="ID" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{72104998-0AC0-4A1D-A3A7-50CD3B2D40DD}" name="Title" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{38A42720-4B21-4E07-B4EF-702C8825CE50}" name="Authors" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{54AD448E-E9F4-4131-8404-BEC167281CF5}" name="Year" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{D230C5A6-1163-47C0-9DD1-691A41D371C1}" name="Venue" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{5E7F9669-4FCF-4C87-9C40-9ABADB67D416}" name="Domain" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{FA66DECF-FA98-42F4-9108-713366B617A8}" name="Problem" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{1F7AB528-8BB9-4231-B183-A5B80AC8ED0C}" name="Method" dataDxfId="11"/>
+    <tableColumn id="9" xr3:uid="{8739A737-0B47-4AF3-872E-3245AD5C6F65}" name="Dataset" dataDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{03BF5615-BD82-42DD-8759-FFCBBEF812D0}" name="Metrics" dataDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{8FBD0AF8-2B73-41E6-91E0-FEC8A6E8A5DE}" name="Limitations" dataDxfId="8"/>
+    <tableColumn id="12" xr3:uid="{1AF66BE9-1FD6-4E70-961D-B109AC2ADA2D}" name="My Ideas" dataDxfId="7"/>
+    <tableColumn id="13" xr3:uid="{DA8FBC99-63EC-4797-BC7F-D07E928AAC42}" name="Status" dataDxfId="6"/>
+    <tableColumn id="14" xr3:uid="{6013D486-8D83-4674-B8E8-BBA01F8D5182}" name="Assumptions" dataDxfId="5"/>
+    <tableColumn id="15" xr3:uid="{8E2F4043-643A-4C29-A6CF-D687803ADB46}" name="Open Questions" dataDxfId="4"/>
     <tableColumn id="16" xr3:uid="{620F6A5A-1B54-49EC-B204-0A0387A762B6}" name="Column16" dataDxfId="3"/>
-    <tableColumn id="17" xr3:uid="{4FDEC39F-1170-4707-BF88-BA3F84BA31E2}" name="Column17" dataDxfId="2"/>
+    <tableColumn id="17" xr3:uid="{4FDEC39F-1170-4707-BF88-BA3F84BA31E2}" name="Priority (High/Medium/Low)" dataDxfId="2"/>
     <tableColumn id="18" xr3:uid="{8BF0A9D8-6901-4BA9-93CB-35BA889098FF}" name="Column18" dataDxfId="1"/>
     <tableColumn id="19" xr3:uid="{B729C20C-0AA0-4F13-9BC5-2698A61F320D}" name="Column19" dataDxfId="0"/>
   </tableColumns>
@@ -963,15 +930,15 @@
     <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.44140625" customWidth="1"/>
+    <col min="6" max="6" width="54.5546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.44140625" customWidth="1"/>
     <col min="9" max="9" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="53.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="65.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="63.44140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="76.21875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="52.44140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="8.109375" bestFit="1" customWidth="1"/>
@@ -979,61 +946,61 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="S1" s="1" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
@@ -1077,57 +1044,55 @@
         <v>12</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>42</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="P2" s="4"/>
       <c r="Q2" s="4" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
     </row>
-    <row r="3" spans="1:21" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="4">
         <v>2017</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
@@ -1139,7 +1104,7 @@
     <row r="4" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4">
@@ -1148,26 +1113,26 @@
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="5"/>
       <c r="K4" s="3"/>
       <c r="L4" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="M4" s="2"/>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
       <c r="U4" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="144" x14ac:dyDescent="0.3">
@@ -1178,10 +1143,10 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="5"/>
@@ -1196,38 +1161,50 @@
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
+      <c r="B6" s="2"/>
       <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
+      <c r="D6" s="2"/>
       <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
+      <c r="L6" s="2"/>
       <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
+      <c r="N6" t="s">
+        <v>39</v>
+      </c>
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
+      <c r="B7" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
+      <c r="D7" s="2">
+        <v>2024</v>
+      </c>
       <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
+      <c r="F7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
+      <c r="K7" t="s">
+        <v>40</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
@@ -1248,7 +1225,7 @@
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
+      <c r="L8" s="2"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
